--- a/ig/main/alignement-nuva-cipucd.xlsx
+++ b/ig/main/alignement-nuva-cipucd.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1144</t>
+    <t>1.0.1164</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07</t>
+    <t>2026-10-05</t>
   </si>
   <si>
     <t>Publisher</t>
